--- a/artfynd/A 881-2025 artfynd.xlsx
+++ b/artfynd/A 881-2025 artfynd.xlsx
@@ -1014,11 +1014,11 @@
         <v>119627148</v>
       </c>
       <c r="B5" t="n">
-        <v>56522</v>
+        <v>56593</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">

--- a/artfynd/A 881-2025 artfynd.xlsx
+++ b/artfynd/A 881-2025 artfynd.xlsx
@@ -1014,7 +1014,7 @@
         <v>119627148</v>
       </c>
       <c r="B5" t="n">
-        <v>56593</v>
+        <v>56594</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
